--- a/Coulomb/Coulomb.xlsx
+++ b/Coulomb/Coulomb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Angolo" sheetId="1" state="visible" r:id="rId5"/>
@@ -325,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -345,7 +345,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -378,11 +377,10 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf fontId="2" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -962,12 +960,12 @@
       <c r="F3" s="10">
         <v>20</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12"/>
+      <c r="A4" s="11"/>
       <c r="B4">
         <v>101</v>
       </c>
@@ -980,189 +978,189 @@
       <c r="E4">
         <v>28</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>18</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>1.e-003</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16">
         <v>99</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>71</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>53</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>31</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>22</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <f>AVERAGE(B3:B5)</f>
         <v>99</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <f t="shared" ref="C7:F7" si="0">AVERAGE(C3:C5)</f>
         <v>69.666666666666671</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <f t="shared" ref="B8:F8" si="1">RADIANS(B7)</f>
         <v>1.7278759594743864</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <f t="shared" si="1"/>
         <v>1.2159127122227162</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <f t="shared" si="1"/>
         <v>0.89011791851710798</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <f t="shared" si="1"/>
         <v>0.50614548307835561</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="23">
         <f t="shared" si="1"/>
         <v>0.3490658503988659</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <f>_xlfn.STDEV.S(B3:B5)</f>
         <v>2</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <f t="shared" ref="C9:F9" si="2">_xlfn.STDEV.S(C3:C5)</f>
         <v>1.5275252316519468</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <f t="shared" si="2"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="25">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="22">
         <f t="shared" ref="B10:F10" si="3">RADIANS(B9)</f>
         <v>3.4906585039886591e-002</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="22">
         <f t="shared" si="3"/>
         <v>2.6660344699615573e-002</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <f t="shared" si="3"/>
         <v>3.4906585039886591e-002</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <f t="shared" si="3"/>
         <v>3.0229989403903628e-002</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="23">
         <f t="shared" si="3"/>
         <v>3.4906585039886591e-002</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="26"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="24">
         <f>B9/SQRT(3)</f>
         <v>1.1547005383792517</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <f>C9/SQRT(3)</f>
         <v>0.88191710368819698</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <f>D9/SQRT(3)</f>
         <v>1.1547005383792517</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <f>E9/SQRT(3)</f>
         <v>1</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="25">
         <f>F9/SQRT(3)</f>
         <v>1.1547005383792517</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="28">
         <f t="shared" ref="B12:F12" si="4">RADIANS(B11)</f>
         <v>2.0153326269269089e-002</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f t="shared" si="4"/>
         <v>1.5392357189011264e-002</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <f t="shared" si="4"/>
         <v>2.0153326269269089e-002</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="28">
         <f t="shared" si="4"/>
         <v>1.7453292519943295e-002</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <f t="shared" si="4"/>
         <v>2.0153326269269089e-002</v>
       </c>
     </row>
     <row r="14" ht="15.75">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <f>B2+$G$2</f>
         <v>9.9000000000000005e-002</v>
       </c>
@@ -1184,22 +1182,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="16">
         <v>1.e-003</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="16">
         <v>1.e-003</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>1.e-003</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>1.e-003</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>1.e-003</v>
       </c>
     </row>
@@ -1228,37 +1226,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="34" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36">
+      <c r="A2" s="35">
         <v>6000</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="22">
         <f t="shared" ref="D2:D9" si="5">RADIANS(C2)</f>
         <v>1.2217304763960306</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="23">
         <f t="shared" ref="E2:E10" si="6">RADIANS(4)</f>
         <v>6.9813170079773182e-002</v>
       </c>
@@ -1267,153 +1265,153 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36">
+      <c r="A3" s="35">
         <v>5500</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>62</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <f t="shared" si="5"/>
         <v>1.0821041362364843</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36">
+      <c r="A4" s="35">
         <v>5000</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>48</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <f t="shared" si="5"/>
         <v>0.83775804095727824</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36">
+      <c r="A5" s="35">
         <v>4500</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>41</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="22">
         <f t="shared" si="5"/>
         <v>0.71558499331767511</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36">
+      <c r="A6" s="35">
         <v>4000</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>35</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <f t="shared" si="5"/>
         <v>0.6108652381980153</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36">
+      <c r="A7" s="35">
         <v>3500</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>23</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <f t="shared" si="5"/>
         <v>0.4014257279586958</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36">
+      <c r="A8" s="35">
         <v>3000</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <f t="shared" si="5"/>
         <v>0.3490658503988659</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36">
+      <c r="A9" s="35">
         <v>2500</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="22">
         <f t="shared" si="5"/>
         <v>0.24434609527920614</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="23">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>2000</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
+        <v>60</v>
+      </c>
+      <c r="C10" s="16">
         <v>10</v>
       </c>
-      <c r="C10" s="17">
-        <v>10</v>
-      </c>
-      <c r="D10" s="29">
+      <c r="D10" s="28">
         <f>RADIANS(C10)</f>
         <v>0.17453292519943295</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <f t="shared" si="6"/>
         <v>6.9813170079773182e-002</v>
       </c>
@@ -1441,201 +1439,201 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="37" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36">
+      <c r="A2" s="35">
         <v>6000</v>
       </c>
-      <c r="B2">
-        <v>10</v>
+      <c r="B2" s="38">
+        <v>60</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="22">
         <f t="shared" ref="D2:D10" si="7">RADIANS(C2)</f>
         <v>1.2217304763960306</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="23">
         <f t="shared" ref="E2:E10" si="8">RADIANS(4)</f>
         <v>6.9813170079773182e-002</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>6000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36">
+      <c r="A3" s="35">
         <v>5500</v>
       </c>
-      <c r="B3">
-        <v>10</v>
+      <c r="B3" s="38">
+        <v>60</v>
       </c>
       <c r="C3">
         <v>65</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <f t="shared" si="7"/>
         <v>1.1344640137963142</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36">
+      <c r="A4" s="35">
         <v>5000</v>
       </c>
-      <c r="B4">
-        <v>10</v>
+      <c r="B4" s="38">
+        <v>60</v>
       </c>
       <c r="C4">
         <v>61</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <f t="shared" si="7"/>
         <v>1.064650843716541</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36">
+      <c r="A5" s="35">
         <v>4500</v>
       </c>
-      <c r="B5">
-        <v>10</v>
+      <c r="B5" s="38">
+        <v>60</v>
       </c>
       <c r="C5">
         <v>59</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="22">
         <f t="shared" si="7"/>
         <v>1.0297442586766545</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36">
+      <c r="A6" s="35">
         <v>4000</v>
       </c>
-      <c r="B6">
-        <v>10</v>
+      <c r="B6" s="38">
+        <v>60</v>
       </c>
       <c r="C6">
         <v>52</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <f t="shared" si="7"/>
         <v>0.90757121103705141</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36">
+      <c r="A7" s="35">
         <v>3500</v>
       </c>
-      <c r="B7">
-        <v>10</v>
+      <c r="B7" s="38">
+        <v>60</v>
       </c>
       <c r="C7">
         <v>43</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <f t="shared" si="7"/>
         <v>0.75049157835756175</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36">
+      <c r="A8" s="35">
         <v>3000</v>
       </c>
-      <c r="B8">
-        <v>10</v>
+      <c r="B8" s="38">
+        <v>60</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <f t="shared" si="7"/>
         <v>0.68067840827778847</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36">
+      <c r="A9" s="35">
         <v>2500</v>
       </c>
-      <c r="B9">
-        <v>10</v>
+      <c r="B9" s="38">
+        <v>60</v>
       </c>
       <c r="C9">
         <v>35</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="22">
         <f t="shared" si="7"/>
         <v>0.6108652381980153</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="23">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>2000</v>
       </c>
-      <c r="B10" s="17">
-        <v>10</v>
-      </c>
-      <c r="C10" s="17">
+      <c r="B10" s="16">
+        <v>60</v>
+      </c>
+      <c r="C10" s="16">
         <v>28</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="28">
         <f t="shared" si="7"/>
         <v>0.48869219055841229</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <f t="shared" si="8"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="H13" s="27"/>
+      <c r="H13" s="26"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1656,96 +1654,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="34" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36">
+      <c r="A2" s="35">
         <f>2*10^(-5)</f>
         <v>2.0000000000000002e-005</v>
       </c>
       <c r="B2">
         <v>136</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="22">
         <f t="shared" ref="C2:C6" si="9">RADIANS(B2)</f>
         <v>2.3736477827122884</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="23">
         <f t="shared" ref="D2:D6" si="10">RADIANS(4)</f>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36">
+      <c r="A3" s="35">
         <v>4.0000000000000003e-005</v>
       </c>
       <c r="B3">
         <v>282</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="22">
         <f t="shared" si="9"/>
         <v>4.9218284906240095</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <f t="shared" si="10"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36">
+      <c r="A4" s="35">
         <v>5.0000000000000002e-005</v>
       </c>
       <c r="B4">
         <v>355</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="22">
         <f t="shared" si="9"/>
         <v>6.1959188445798699</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <f t="shared" si="10"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36">
+      <c r="A5" s="35">
         <v>6.9999999999999994e-005</v>
       </c>
       <c r="B5">
         <v>500</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="22">
         <f t="shared" si="9"/>
         <v>8.7266462599716483</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <f t="shared" si="10"/>
         <v>6.9813170079773182e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>9.0000000000000006e-005</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="39">
         <v>645</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <f t="shared" si="9"/>
         <v>11.257373675363425</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <f t="shared" si="10"/>
         <v>6.9813170079773182e-002</v>
       </c>

--- a/Coulomb/Coulomb.xlsx
+++ b/Coulomb/Coulomb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Angolo" sheetId="1" state="visible" r:id="rId5"/>
@@ -376,11 +376,11 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="2" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="2" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1246,7 +1246,7 @@
       <c r="A2" s="35">
         <v>6000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="36">
         <v>60</v>
       </c>
       <c r="C2">
@@ -1268,8 +1268,8 @@
       <c r="A3" s="35">
         <v>5500</v>
       </c>
-      <c r="B3">
-        <v>60</v>
+      <c r="B3" s="36">
+        <v>55</v>
       </c>
       <c r="C3">
         <v>62</v>
@@ -1287,8 +1287,8 @@
       <c r="A4" s="35">
         <v>5000</v>
       </c>
-      <c r="B4">
-        <v>60</v>
+      <c r="B4" s="36">
+        <v>50</v>
       </c>
       <c r="C4">
         <v>48</v>
@@ -1306,8 +1306,8 @@
       <c r="A5" s="35">
         <v>4500</v>
       </c>
-      <c r="B5">
-        <v>60</v>
+      <c r="B5" s="36">
+        <v>45</v>
       </c>
       <c r="C5">
         <v>41</v>
@@ -1325,8 +1325,8 @@
       <c r="A6" s="35">
         <v>4000</v>
       </c>
-      <c r="B6">
-        <v>60</v>
+      <c r="B6" s="36">
+        <v>40</v>
       </c>
       <c r="C6">
         <v>35</v>
@@ -1344,8 +1344,8 @@
       <c r="A7" s="35">
         <v>3500</v>
       </c>
-      <c r="B7">
-        <v>60</v>
+      <c r="B7" s="36">
+        <v>35</v>
       </c>
       <c r="C7">
         <v>23</v>
@@ -1363,8 +1363,8 @@
       <c r="A8" s="35">
         <v>3000</v>
       </c>
-      <c r="B8">
-        <v>60</v>
+      <c r="B8" s="36">
+        <v>30</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -1382,8 +1382,8 @@
       <c r="A9" s="35">
         <v>2500</v>
       </c>
-      <c r="B9">
-        <v>60</v>
+      <c r="B9" s="36">
+        <v>25</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -1398,11 +1398,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36">
+      <c r="A10" s="37">
         <v>2000</v>
       </c>
       <c r="B10" s="16">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C10" s="16">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       <c r="E1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="38" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="A2" s="35">
         <v>6000</v>
       </c>
-      <c r="B2" s="38">
+      <c r="B2" s="36">
         <v>60</v>
       </c>
       <c r="C2">
@@ -1484,8 +1484,8 @@
       <c r="A3" s="35">
         <v>5500</v>
       </c>
-      <c r="B3" s="38">
-        <v>60</v>
+      <c r="B3" s="36">
+        <v>55</v>
       </c>
       <c r="C3">
         <v>65</v>
@@ -1503,8 +1503,8 @@
       <c r="A4" s="35">
         <v>5000</v>
       </c>
-      <c r="B4" s="38">
-        <v>60</v>
+      <c r="B4" s="36">
+        <v>50</v>
       </c>
       <c r="C4">
         <v>61</v>
@@ -1522,8 +1522,8 @@
       <c r="A5" s="35">
         <v>4500</v>
       </c>
-      <c r="B5" s="38">
-        <v>60</v>
+      <c r="B5" s="36">
+        <v>45</v>
       </c>
       <c r="C5">
         <v>59</v>
@@ -1541,8 +1541,8 @@
       <c r="A6" s="35">
         <v>4000</v>
       </c>
-      <c r="B6" s="38">
-        <v>60</v>
+      <c r="B6" s="36">
+        <v>40</v>
       </c>
       <c r="C6">
         <v>52</v>
@@ -1560,8 +1560,8 @@
       <c r="A7" s="35">
         <v>3500</v>
       </c>
-      <c r="B7" s="38">
-        <v>60</v>
+      <c r="B7" s="36">
+        <v>35</v>
       </c>
       <c r="C7">
         <v>43</v>
@@ -1579,8 +1579,8 @@
       <c r="A8" s="35">
         <v>3000</v>
       </c>
-      <c r="B8" s="38">
-        <v>60</v>
+      <c r="B8" s="36">
+        <v>30</v>
       </c>
       <c r="C8">
         <v>39</v>
@@ -1598,8 +1598,8 @@
       <c r="A9" s="35">
         <v>2500</v>
       </c>
-      <c r="B9" s="38">
-        <v>60</v>
+      <c r="B9" s="36">
+        <v>25</v>
       </c>
       <c r="C9">
         <v>35</v>
@@ -1614,11 +1614,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36">
+      <c r="A10" s="37">
         <v>2000</v>
       </c>
       <c r="B10" s="16">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C10" s="16">
         <v>28</v>
@@ -1733,7 +1733,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36">
+      <c r="A6" s="37">
         <v>9.0000000000000006e-005</v>
       </c>
       <c r="B6" s="39">
